--- a/Data/Excel/npc.xlsx
+++ b/Data/Excel/npc.xlsx
@@ -609,7 +609,7 @@
     <row r="5" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
-        <v>1001</v>
+        <v>41000001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>24</v>
@@ -651,7 +651,7 @@
     <row r="6" spans="1:14">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
-        <v>1002</v>
+        <v>41000002</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>26</v>
@@ -687,7 +687,7 @@
     <row r="7" spans="1:14">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
-        <v>2001</v>
+        <v>40200001</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>28</v>
